--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127834644</v>
+        <v>136639585</v>
       </c>
       <c r="B3" t="n">
-        <v>57966</v>
+        <v>91588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,49 +799,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>5741</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ävrö, Sm</t>
+          <t>Sörö, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600421</v>
+        <v>600358</v>
       </c>
       <c r="R3" t="n">
-        <v>6365452</v>
+        <v>6365553</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +864,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,33 +905,33 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834644</t>
+          <t>https://artportalen.se/Sighting/136639585</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127834567</v>
+        <v>127834644</v>
       </c>
       <c r="B4" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -939,7 +948,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -949,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600425</v>
+        <v>600421</v>
       </c>
       <c r="R4" t="n">
-        <v>6365545</v>
+        <v>6365452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,12 +988,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,19 +1013,19 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834567</t>
+          <t>https://artportalen.se/Sighting/127834644</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127834646</v>
+        <v>127834567</v>
       </c>
       <c r="B5" t="n">
         <v>57950</v>
@@ -1063,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600493</v>
+        <v>600425</v>
       </c>
       <c r="R5" t="n">
-        <v>6365582</v>
+        <v>6365545</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,12 +1102,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,22 +1127,22 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834646</t>
+          <t>https://artportalen.se/Sighting/127834567</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130826523</v>
+        <v>127834646</v>
       </c>
       <c r="B6" t="n">
-        <v>56614</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,16 +1150,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100084</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1163,31 +1172,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600405</v>
+        <v>600493</v>
       </c>
       <c r="R6" t="n">
-        <v>6365471</v>
+        <v>6365582</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,17 +1216,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hasselmusbo i örnbräken,  ~8cm diameter</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,27 +1236,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130826523</t>
+          <t>https://artportalen.se/Sighting/127834646</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136039724</v>
+        <v>130826523</v>
       </c>
       <c r="B7" t="n">
-        <v>57807</v>
+        <v>56614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,21 +1264,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102118</v>
+        <v>100084</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Muscardinus avellanarius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1289,14 +1286,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1305,13 +1307,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600376</v>
+        <v>600405</v>
       </c>
       <c r="R7" t="n">
-        <v>6365429</v>
+        <v>6365471</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,12 +1337,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hasselmusbo i örnbräken,  ~8cm diameter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,27 +1362,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136039724</t>
+          <t>https://artportalen.se/Sighting/130826523</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127834594</v>
+        <v>136039724</v>
       </c>
       <c r="B8" t="n">
-        <v>58286</v>
+        <v>57807</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,21 +1390,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103008</v>
+        <v>102118</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,27 +1412,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600724</v>
+        <v>600376</v>
       </c>
       <c r="R8" t="n">
-        <v>6365663</v>
+        <v>6365429</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1449,12 +1458,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,33 +1489,33 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834594</t>
+          <t>https://artportalen.se/Sighting/136039724</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127834597</v>
+        <v>127834594</v>
       </c>
       <c r="B9" t="n">
-        <v>58602</v>
+        <v>58286</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103042</v>
+        <v>103008</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1519,21 +1528,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600351</v>
+        <v>600724</v>
       </c>
       <c r="R9" t="n">
-        <v>6365493</v>
+        <v>6365663</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,33 +1603,33 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834597</t>
+          <t>https://artportalen.se/Sighting/127834594</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136125153</v>
+        <v>127834597</v>
       </c>
       <c r="B10" t="n">
-        <v>58843</v>
+        <v>58602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208245</v>
+        <v>103042</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1630,25 +1642,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sörö, Sm</t>
+          <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600332</v>
+        <v>600351</v>
       </c>
       <c r="R10" t="n">
-        <v>6365561</v>
+        <v>6365493</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,22 +1683,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:17</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:17</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,51 +1714,64 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136125153</t>
+          <t>https://artportalen.se/Sighting/127834597</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127835957</v>
+        <v>136125153</v>
       </c>
       <c r="B11" t="n">
-        <v>111390</v>
+        <v>58843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>208245</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ävrö, Sm</t>
+          <t>Sörö, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600357</v>
+        <v>600332</v>
       </c>
       <c r="R11" t="n">
-        <v>6365478</v>
+        <v>6365561</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,12 +1798,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,44 +1828,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127835957</t>
+          <t>https://artportalen.se/Sighting/136125153</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127834130</v>
+        <v>127835957</v>
       </c>
       <c r="B12" t="n">
-        <v>106156</v>
+        <v>111390</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221141</v>
+        <v>219711</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1859,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600345</v>
+        <v>600357</v>
       </c>
       <c r="R12" t="n">
-        <v>6365475</v>
+        <v>6365478</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,12 +1910,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,7 +1924,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1915,19 +1935,19 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834130</t>
+          <t>https://artportalen.se/Sighting/127835957</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127834131</v>
+        <v>127834130</v>
       </c>
       <c r="B13" t="n">
         <v>106156</v>
@@ -1962,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600354</v>
+        <v>600345</v>
       </c>
       <c r="R13" t="n">
-        <v>6365478</v>
+        <v>6365475</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,13 +2044,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834131</t>
+          <t>https://artportalen.se/Sighting/127834130</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127834132</v>
+        <v>127834131</v>
       </c>
       <c r="B14" t="n">
         <v>106156</v>
@@ -2065,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600357</v>
+        <v>600354</v>
       </c>
       <c r="R14" t="n">
-        <v>6365492</v>
+        <v>6365478</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,13 +2147,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834132</t>
+          <t>https://artportalen.se/Sighting/127834131</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127834134</v>
+        <v>127834132</v>
       </c>
       <c r="B15" t="n">
         <v>106156</v>
@@ -2168,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600352</v>
+        <v>600357</v>
       </c>
       <c r="R15" t="n">
-        <v>6365506</v>
+        <v>6365492</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2230,13 +2250,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834134</t>
+          <t>https://artportalen.se/Sighting/127834132</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127834235</v>
+        <v>127834134</v>
       </c>
       <c r="B16" t="n">
         <v>106156</v>
@@ -2271,10 +2291,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600340</v>
+        <v>600352</v>
       </c>
       <c r="R16" t="n">
-        <v>6365481</v>
+        <v>6365506</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,17 +2321,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,6 +2335,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2331,22 +2347,22 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834235</t>
+          <t>https://artportalen.se/Sighting/127834134</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127834133</v>
+        <v>127834235</v>
       </c>
       <c r="B17" t="n">
-        <v>101326</v>
+        <v>106156</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,21 +2370,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2378,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600354</v>
+        <v>600340</v>
       </c>
       <c r="R17" t="n">
-        <v>6365500</v>
+        <v>6365481</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2408,12 +2424,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,19 +2454,19 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834133</t>
+          <t>https://artportalen.se/Sighting/127834235</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127834135</v>
+        <v>127834133</v>
       </c>
       <c r="B18" t="n">
         <v>101326</v>
@@ -2480,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600339</v>
+        <v>600354</v>
       </c>
       <c r="R18" t="n">
-        <v>6365499</v>
+        <v>6365500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,13 +2562,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834135</t>
+          <t>https://artportalen.se/Sighting/127834133</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127834157</v>
+        <v>127834135</v>
       </c>
       <c r="B19" t="n">
         <v>101326</v>
@@ -2582,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600540</v>
+        <v>600339</v>
       </c>
       <c r="R19" t="n">
-        <v>6365576</v>
+        <v>6365499</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2612,12 +2633,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2642,6 +2663,108 @@
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834135</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127834157</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ävrö, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>600540</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6365576</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127834157</t>
         </is>
@@ -2667,6 +2790,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>136639585</v>
       </c>
       <c r="B3" t="n">
-        <v>91588</v>
+        <v>91590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>136639585</v>
       </c>
       <c r="B3" t="n">
-        <v>91590</v>
+        <v>91592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>136125153</v>
       </c>
       <c r="B11" t="n">
-        <v>58843</v>
+        <v>58845</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>136639585</v>
       </c>
       <c r="B3" t="n">
-        <v>91592</v>
+        <v>91594</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>136639585</v>
       </c>
       <c r="B3" t="n">
-        <v>91594</v>
+        <v>91596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>136639585</v>
       </c>
       <c r="B3" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>136639585</v>
       </c>
       <c r="B3" t="n">
-        <v>91598</v>
+        <v>91599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>136639585</v>
       </c>
       <c r="B3" t="n">
-        <v>91599</v>
+        <v>91605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>136639585</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
+        <v>91609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>136639585</v>
       </c>
       <c r="B3" t="n">
-        <v>91609</v>
+        <v>91611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>136639585</v>
       </c>
       <c r="B3" t="n">
-        <v>91611</v>
+        <v>91624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>136639585</v>
       </c>
       <c r="B3" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1845,48 +1845,52 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127835957</v>
+        <v>137453421</v>
       </c>
       <c r="B12" t="n">
-        <v>111390</v>
+        <v>56955</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219711</v>
+        <v>208257</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600357</v>
+        <v>600363</v>
       </c>
       <c r="R12" t="n">
-        <v>6365478</v>
+        <v>6365444</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,12 +1914,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Under platta vid fördjupad inventering.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,22 +1944,22 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127835957</t>
+          <t>https://artportalen.se/Sighting/137453421</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127834130</v>
+        <v>137453422</v>
       </c>
       <c r="B13" t="n">
-        <v>106156</v>
+        <v>56955</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,37 +1967,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221141</v>
+        <v>208257</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ävrö, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600345</v>
+        <v>600372</v>
       </c>
       <c r="R13" t="n">
-        <v>6365475</v>
+        <v>6365592</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,12 +2025,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Under platta vid fördjupad inventering.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,7 +2044,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2038,39 +2055,39 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834130</t>
+          <t>https://artportalen.se/Sighting/137453422</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127834131</v>
+        <v>127835957</v>
       </c>
       <c r="B14" t="n">
-        <v>106156</v>
+        <v>111390</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221141</v>
+        <v>219711</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2085,7 +2102,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600354</v>
+        <v>600357</v>
       </c>
       <c r="R14" t="n">
         <v>6365478</v>
@@ -2115,12 +2132,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,7 +2146,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2141,19 +2157,19 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834131</t>
+          <t>https://artportalen.se/Sighting/127835957</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127834132</v>
+        <v>127834130</v>
       </c>
       <c r="B15" t="n">
         <v>106156</v>
@@ -2188,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600357</v>
+        <v>600345</v>
       </c>
       <c r="R15" t="n">
-        <v>6365492</v>
+        <v>6365475</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,13 +2266,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834132</t>
+          <t>https://artportalen.se/Sighting/127834130</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127834134</v>
+        <v>127834131</v>
       </c>
       <c r="B16" t="n">
         <v>106156</v>
@@ -2291,10 +2307,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600352</v>
+        <v>600354</v>
       </c>
       <c r="R16" t="n">
-        <v>6365506</v>
+        <v>6365478</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,13 +2369,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834134</t>
+          <t>https://artportalen.se/Sighting/127834131</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127834235</v>
+        <v>127834132</v>
       </c>
       <c r="B17" t="n">
         <v>106156</v>
@@ -2394,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600340</v>
+        <v>600357</v>
       </c>
       <c r="R17" t="n">
-        <v>6365481</v>
+        <v>6365492</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2424,17 +2440,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,6 +2454,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2454,22 +2466,22 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834235</t>
+          <t>https://artportalen.se/Sighting/127834132</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127834133</v>
+        <v>127834134</v>
       </c>
       <c r="B18" t="n">
-        <v>101326</v>
+        <v>106156</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2477,21 +2489,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2501,10 +2513,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600354</v>
+        <v>600352</v>
       </c>
       <c r="R18" t="n">
-        <v>6365500</v>
+        <v>6365506</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2545,6 +2557,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2562,16 +2575,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834133</t>
+          <t>https://artportalen.se/Sighting/127834134</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127834135</v>
+        <v>127834235</v>
       </c>
       <c r="B19" t="n">
-        <v>101326</v>
+        <v>106156</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,21 +2592,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2603,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600339</v>
+        <v>600340</v>
       </c>
       <c r="R19" t="n">
-        <v>6365499</v>
+        <v>6365481</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2633,12 +2646,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2658,19 +2676,19 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127834135</t>
+          <t>https://artportalen.se/Sighting/127834235</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127834157</v>
+        <v>127834133</v>
       </c>
       <c r="B20" t="n">
         <v>101326</v>
@@ -2705,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600540</v>
+        <v>600354</v>
       </c>
       <c r="R20" t="n">
-        <v>6365576</v>
+        <v>6365500</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2735,12 +2753,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,6 +2783,210 @@
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834133</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127834135</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ävrö, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>600339</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6365499</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127834135</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127834157</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ävrö, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>600540</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6365576</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127834157</t>
         </is>
@@ -2791,6 +3013,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9633-2025 artfynd.xlsx
+++ b/artfynd/A 9633-2025 artfynd.xlsx
@@ -1848,7 +1848,7 @@
         <v>137453421</v>
       </c>
       <c r="B12" t="n">
-        <v>56955</v>
+        <v>56958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>137453422</v>
       </c>
       <c r="B13" t="n">
-        <v>56955</v>
+        <v>56958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
